--- a/excel/100(n)/AVG_ReverseSort_Dataset.xlsx
+++ b/excel/100(n)/AVG_ReverseSort_Dataset.xlsx
@@ -102,19 +102,19 @@
         <v>100.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>196110.0</v>
+        <v>9357.8</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>85170.0</v>
+        <v>5229.8</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>75350.0</v>
+        <v>10395.3</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>25110.0</v>
+        <v>11653.5</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>29700.0</v>
+        <v>10890.4</v>
       </c>
     </row>
   </sheetData>
